--- a/data/file_generation/input/data_60/1.xlsx
+++ b/data/file_generation/input/data_60/1.xlsx
@@ -1725,26 +1725,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E211D68-D7E3-4F04-9498-1BBEA2E32079}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55083D7A-3C6A-442E-99A2-B6F6F0B72EB3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC49A68-BEF5-4743-A745-14C136C1ACB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156209DB-13CA-4017-87FE-D0D754D822EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D036358B-15BD-4AC4-934C-BD8B0034AA25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D821A931-CD58-4F07-8860-ED8487768FF2}"/>
 </file>